--- a/ProductionBuild/fullviewhealth.result.xlsx
+++ b/ProductionBuild/fullviewhealth.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ47"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -477,60 +477,65 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>avgdividend</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>totaldividends</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>price_start</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>price_end</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>totalreturn</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>totalreturnover10</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>shares500</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>totalspend</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>fiveyearequityproj</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>fiveyeardivproj</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>totalfiveyearview</t>
         </is>
@@ -605,40 +610,45 @@
       <c r="W2">
         <v>0.834</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z2">
         <v>1.1849</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>11.849</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>25</v>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <v>30.45000076293945</v>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <v>5.450000762939453</v>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <v>17.29900076293945</v>
       </c>
-      <c r="AE2">
+      <c r="AF2">
         <v>1.729900076293945</v>
       </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>17</v>
       </c>
-      <c r="AG2">
+      <c r="AH2">
         <v>517.6500129699707</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>8.649500381469727</v>
       </c>
-      <c r="AI2">
+      <c r="AJ2">
         <v>5.9245</v>
       </c>
-      <c r="AJ2">
+      <c r="AK2">
         <v>14.57400038146973</v>
       </c>
     </row>
@@ -711,40 +721,45 @@
       <c r="W3">
         <v>1.707</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z3">
         <v>1.1421</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>11.421</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>16.47999954223633</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <v>45.83000183105469</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>29.35000228881836</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>40.77100228881836</v>
       </c>
-      <c r="AE3">
+      <c r="AF3">
         <v>4.077100228881836</v>
       </c>
-      <c r="AF3">
+      <c r="AG3">
         <v>11</v>
       </c>
-      <c r="AG3">
+      <c r="AH3">
         <v>504.1300201416016</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>20.38550114440918</v>
       </c>
-      <c r="AI3">
+      <c r="AJ3">
         <v>5.710500000000001</v>
       </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>26.09600114440918</v>
       </c>
     </row>
@@ -817,40 +832,45 @@
       <c r="W4">
         <v>0.545</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z4">
         <v>0.9964000000000001</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>9.964</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>21.84000015258789</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <v>26.39999961853027</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>4.559999465942383</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>14.52399946594238</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>1.452399946594238</v>
       </c>
-      <c r="AF4">
+      <c r="AG4">
         <v>19</v>
       </c>
-      <c r="AG4">
+      <c r="AH4">
         <v>501.5999927520752</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>7.261999732971192</v>
       </c>
-      <c r="AI4">
+      <c r="AJ4">
         <v>4.982</v>
       </c>
-      <c r="AJ4">
+      <c r="AK4">
         <v>12.24399973297119</v>
       </c>
     </row>
@@ -926,40 +946,45 @@
       <c r="X5">
         <v>0.48</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z5">
         <v>1.564545454545454</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>17.21</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>16.48999977111816</v>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <v>18.95999908447266</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>2.469999313354492</v>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>19.67999931335449</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>1.967999931335449</v>
       </c>
-      <c r="AF5">
+      <c r="AG5">
         <v>27</v>
       </c>
-      <c r="AG5">
+      <c r="AH5">
         <v>511.9199752807617</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>9.839999656677247</v>
       </c>
-      <c r="AI5">
+      <c r="AJ5">
         <v>7.822727272727272</v>
       </c>
-      <c r="AJ5">
+      <c r="AK5">
         <v>17.66272692940452</v>
       </c>
     </row>
@@ -1035,40 +1060,45 @@
       <c r="X6">
         <v>0.37</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z6">
         <v>0.9781818181818183</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>10.76</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>35.7400016784668</v>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <v>37.56000137329102</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>1.819999694824219</v>
       </c>
-      <c r="AD6">
+      <c r="AE6">
         <v>12.57999969482422</v>
       </c>
-      <c r="AE6">
+      <c r="AF6">
         <v>1.257999969482422</v>
       </c>
-      <c r="AF6">
+      <c r="AG6">
         <v>14</v>
       </c>
-      <c r="AG6">
+      <c r="AH6">
         <v>525.8400192260742</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>6.289999847412108</v>
       </c>
-      <c r="AI6">
+      <c r="AJ6">
         <v>4.890909090909092</v>
       </c>
-      <c r="AJ6">
+      <c r="AK6">
         <v>11.1809089383212</v>
       </c>
     </row>
@@ -1144,40 +1174,45 @@
       <c r="X7">
         <v>0.699</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z7">
         <v>0.9795454545454545</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>10.775</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>15.53947353363037</v>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <v>17.19000053405762</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>1.650527000427246</v>
       </c>
-      <c r="AD7">
+      <c r="AE7">
         <v>12.42552700042725</v>
       </c>
-      <c r="AE7">
+      <c r="AF7">
         <v>1.242552700042725</v>
       </c>
-      <c r="AF7">
+      <c r="AG7">
         <v>30</v>
       </c>
-      <c r="AG7">
+      <c r="AH7">
         <v>515.7000160217285</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>6.212763500213622</v>
       </c>
-      <c r="AI7">
+      <c r="AJ7">
         <v>4.897727272727272</v>
       </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>11.1104907729409</v>
       </c>
     </row>
@@ -1250,40 +1285,45 @@
       <c r="W8">
         <v>2.436</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z8">
         <v>1.6056</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>16.056</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>25.20000076293945</v>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <v>49.31000137329102</v>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <v>24.11000061035156</v>
       </c>
-      <c r="AD8">
+      <c r="AE8">
         <v>40.16600061035156</v>
       </c>
-      <c r="AE8">
+      <c r="AF8">
         <v>4.016600061035156</v>
       </c>
-      <c r="AF8">
+      <c r="AG8">
         <v>11</v>
       </c>
-      <c r="AG8">
+      <c r="AH8">
         <v>542.4100151062012</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>20.08300030517578</v>
       </c>
-      <c r="AI8">
+      <c r="AJ8">
         <v>8.027999999999999</v>
       </c>
-      <c r="AJ8">
+      <c r="AK8">
         <v>28.11100030517578</v>
       </c>
     </row>
@@ -1359,40 +1399,45 @@
       <c r="X9">
         <v>0.708</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z9">
         <v>0.4082727272727272</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>4.491</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>6.769999980926514</v>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <v>22.46999931335449</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>15.69999933242798</v>
       </c>
-      <c r="AD9">
+      <c r="AE9">
         <v>20.19099933242798</v>
       </c>
-      <c r="AE9">
+      <c r="AF9">
         <v>2.019099933242798</v>
       </c>
-      <c r="AF9">
+      <c r="AG9">
         <v>23</v>
       </c>
-      <c r="AG9">
+      <c r="AH9">
         <v>516.8099842071533</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>10.09549966621399</v>
       </c>
-      <c r="AI9">
+      <c r="AJ9">
         <v>2.041363636363636</v>
       </c>
-      <c r="AJ9">
+      <c r="AK9">
         <v>12.13686330257763</v>
       </c>
     </row>
@@ -1465,40 +1510,45 @@
       <c r="X10">
         <v>2.183</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z10">
         <v>1.3828666</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>13.828666</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>23.48333358764648</v>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <v>39.20000076293945</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>15.71666717529297</v>
       </c>
-      <c r="AD10">
+      <c r="AE10">
         <v>29.54533317529297</v>
       </c>
-      <c r="AE10">
+      <c r="AF10">
         <v>2.954533317529297</v>
       </c>
-      <c r="AF10">
+      <c r="AG10">
         <v>13</v>
       </c>
-      <c r="AG10">
+      <c r="AH10">
         <v>509.6000099182129</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>14.77266658764648</v>
       </c>
-      <c r="AI10">
+      <c r="AJ10">
         <v>6.914333</v>
       </c>
-      <c r="AJ10">
+      <c r="AK10">
         <v>21.68699958764648</v>
       </c>
     </row>
@@ -1574,40 +1624,45 @@
       <c r="X11">
         <v>0.33</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z11">
         <v>1.26</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>13.86</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>39.58000183105469</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <v>27.23999977111816</v>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <v>-12.34000205993652</v>
       </c>
-      <c r="AD11">
+      <c r="AE11">
         <v>1.519997940063478</v>
       </c>
-      <c r="AE11">
+      <c r="AF11">
         <v>0.1519997940063478</v>
       </c>
-      <c r="AF11">
+      <c r="AG11">
         <v>19</v>
       </c>
-      <c r="AG11">
+      <c r="AH11">
         <v>517.5599956512451</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>0.7599989700317389</v>
       </c>
-      <c r="AI11">
+      <c r="AJ11">
         <v>6.3</v>
       </c>
-      <c r="AJ11">
+      <c r="AK11">
         <v>7.059998970031739</v>
       </c>
     </row>
@@ -1677,40 +1732,45 @@
       <c r="W12">
         <v>2.708</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z12">
         <v>1.915888888888889</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>17.243</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>31.85000038146973</v>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <v>53.41999816894531</v>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <v>21.56999778747559</v>
       </c>
-      <c r="AD12">
+      <c r="AE12">
         <v>38.81299778747559</v>
       </c>
-      <c r="AE12">
+      <c r="AF12">
         <v>3.881299778747559</v>
       </c>
-      <c r="AF12">
+      <c r="AG12">
         <v>10</v>
       </c>
-      <c r="AG12">
+      <c r="AH12">
         <v>534.1999816894531</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>19.40649889373779</v>
       </c>
-      <c r="AI12">
+      <c r="AJ12">
         <v>9.579444444444444</v>
       </c>
-      <c r="AJ12">
+      <c r="AK12">
         <v>28.98594333818224</v>
       </c>
     </row>
@@ -1783,40 +1843,45 @@
       <c r="W13">
         <v>2.283</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z13">
         <v>2.5806</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>25.806</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>55.68000030517578</v>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <v>75.87000274658203</v>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <v>20.19000244140625</v>
       </c>
-      <c r="AD13">
+      <c r="AE13">
         <v>45.99600244140625</v>
       </c>
-      <c r="AE13">
+      <c r="AF13">
         <v>4.599600244140625</v>
       </c>
-      <c r="AF13">
+      <c r="AG13">
         <v>7</v>
       </c>
-      <c r="AG13">
+      <c r="AH13">
         <v>531.0900192260742</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>22.99800122070312</v>
       </c>
-      <c r="AI13">
+      <c r="AJ13">
         <v>12.903</v>
       </c>
-      <c r="AJ13">
+      <c r="AK13">
         <v>35.90100122070312</v>
       </c>
     </row>
@@ -1886,40 +1951,45 @@
       <c r="W14">
         <v>1.329</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z14">
         <v>1.117222222222222</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>10.055</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>21.8700008392334</v>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <v>34.15999984741211</v>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <v>12.28999900817871</v>
       </c>
-      <c r="AD14">
+      <c r="AE14">
         <v>22.34499900817871</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>2.234499900817871</v>
       </c>
-      <c r="AF14">
+      <c r="AG14">
         <v>15</v>
       </c>
-      <c r="AG14">
+      <c r="AH14">
         <v>512.3999977111816</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>11.17249950408936</v>
       </c>
-      <c r="AI14">
+      <c r="AJ14">
         <v>5.58611111111111</v>
       </c>
-      <c r="AJ14">
+      <c r="AK14">
         <v>16.75861061520047</v>
       </c>
     </row>
@@ -1965,22 +2035,27 @@
       <c r="X15">
         <v>0.77</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z15">
         <v>2.218333333333333</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>13.31</v>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <v>24.17000007629395</v>
       </c>
-      <c r="AF15">
+      <c r="AG15">
         <v>21</v>
       </c>
-      <c r="AG15">
+      <c r="AH15">
         <v>507.5700016021729</v>
       </c>
-      <c r="AI15">
+      <c r="AJ15">
         <v>11.09166666666667</v>
       </c>
     </row>
@@ -2056,40 +2131,45 @@
       <c r="X16">
         <v>1.218</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z16">
         <v>2.433545454545455</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>26.769</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <v>36.68000030517578</v>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <v>73.20999908447266</v>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <v>36.52999877929688</v>
       </c>
-      <c r="AD16">
+      <c r="AE16">
         <v>63.29899877929688</v>
       </c>
-      <c r="AE16">
+      <c r="AF16">
         <v>6.329899877929688</v>
       </c>
-      <c r="AF16">
+      <c r="AG16">
         <v>7</v>
       </c>
-      <c r="AG16">
+      <c r="AH16">
         <v>512.4699935913086</v>
       </c>
-      <c r="AH16">
+      <c r="AI16">
         <v>31.64949938964844</v>
       </c>
-      <c r="AI16">
+      <c r="AJ16">
         <v>12.16772727272727</v>
       </c>
-      <c r="AJ16">
+      <c r="AK16">
         <v>43.81722666237572</v>
       </c>
     </row>
@@ -2165,40 +2245,45 @@
       <c r="X17">
         <v>2.48</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z17">
         <v>2.987272727272727</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>32.86</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>41.5</v>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <v>48.16999816894531</v>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <v>6.669998168945313</v>
       </c>
-      <c r="AD17">
+      <c r="AE17">
         <v>39.52999816894531</v>
       </c>
-      <c r="AE17">
+      <c r="AF17">
         <v>3.952999816894531</v>
       </c>
-      <c r="AF17">
+      <c r="AG17">
         <v>11</v>
       </c>
-      <c r="AG17">
+      <c r="AH17">
         <v>529.8699798583984</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>19.76499908447266</v>
       </c>
-      <c r="AI17">
+      <c r="AJ17">
         <v>14.93636363636364</v>
       </c>
-      <c r="AJ17">
+      <c r="AK17">
         <v>34.70136272083629</v>
       </c>
     </row>
@@ -2274,40 +2359,45 @@
       <c r="X18">
         <v>0.37</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z18">
         <v>1.171818181818182</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>12.89</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>44.68000030517578</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>29.09000015258789</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>-15.59000015258789</v>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>-2.70000015258789</v>
       </c>
-      <c r="AE18">
+      <c r="AF18">
         <v>-0.270000015258789</v>
       </c>
-      <c r="AF18">
+      <c r="AG18">
         <v>18</v>
       </c>
-      <c r="AG18">
+      <c r="AH18">
         <v>523.620002746582</v>
       </c>
-      <c r="AH18">
+      <c r="AI18">
         <v>-1.350000076293945</v>
       </c>
-      <c r="AI18">
+      <c r="AJ18">
         <v>5.859090909090909</v>
       </c>
-      <c r="AJ18">
+      <c r="AK18">
         <v>4.509090832796964</v>
       </c>
     </row>
@@ -2383,40 +2473,45 @@
       <c r="X19">
         <v>2.535</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z19">
         <v>3.441421636363637</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <v>37.855638</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>43.40909194946289</v>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <v>179.1499938964844</v>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <v>135.7409019470215</v>
       </c>
-      <c r="AD19">
+      <c r="AE19">
         <v>173.5965399470215</v>
       </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>17.35965399470215</v>
       </c>
-      <c r="AF19">
+      <c r="AG19">
         <v>3</v>
       </c>
-      <c r="AG19">
+      <c r="AH19">
         <v>537.4499816894531</v>
       </c>
-      <c r="AH19">
+      <c r="AI19">
         <v>86.79826997351074</v>
       </c>
-      <c r="AI19">
+      <c r="AJ19">
         <v>17.20710818181818</v>
       </c>
-      <c r="AJ19">
+      <c r="AK19">
         <v>104.0053781553289</v>
       </c>
     </row>
@@ -2489,40 +2584,45 @@
       <c r="X20">
         <v>1.765</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z20">
         <v>0.7968000000000001</v>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <v>7.968</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>15.18000030517578</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>25.79999923706055</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>10.61999893188477</v>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <v>18.58799893188477</v>
       </c>
-      <c r="AE20">
+      <c r="AF20">
         <v>1.858799893188477</v>
       </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>20</v>
       </c>
-      <c r="AG20">
+      <c r="AH20">
         <v>515.9999847412109</v>
       </c>
-      <c r="AH20">
+      <c r="AI20">
         <v>9.293999465942383</v>
       </c>
-      <c r="AI20">
+      <c r="AJ20">
         <v>3.984</v>
       </c>
-      <c r="AJ20">
+      <c r="AK20">
         <v>13.27799946594238</v>
       </c>
     </row>
@@ -2598,40 +2698,45 @@
       <c r="X21">
         <v>0.52</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z21">
         <v>1.269100090909091</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>13.960101</v>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <v>22.73556709289551</v>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <v>50.68000030517578</v>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <v>27.94443321228027</v>
       </c>
-      <c r="AD21">
+      <c r="AE21">
         <v>41.90453421228028</v>
       </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>4.190453421228027</v>
       </c>
-      <c r="AF21">
+      <c r="AG21">
         <v>10</v>
       </c>
-      <c r="AG21">
+      <c r="AH21">
         <v>506.8000030517578</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>20.95226710614014</v>
       </c>
-      <c r="AI21">
+      <c r="AJ21">
         <v>6.345500454545454</v>
       </c>
-      <c r="AJ21">
+      <c r="AK21">
         <v>27.29776756068559</v>
       </c>
     </row>
@@ -2707,40 +2812,45 @@
       <c r="X22">
         <v>0.155</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z22">
         <v>0.4990909090909091</v>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <v>5.49</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>13.22000026702881</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>16.96999931335449</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>3.749999046325684</v>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <v>9.239999046325684</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>0.9239999046325684</v>
       </c>
-      <c r="AF22">
+      <c r="AG22">
         <v>30</v>
       </c>
-      <c r="AG22">
+      <c r="AH22">
         <v>509.0999794006348</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>4.619999523162842</v>
       </c>
-      <c r="AI22">
+      <c r="AJ22">
         <v>2.495454545454546</v>
       </c>
-      <c r="AJ22">
+      <c r="AK22">
         <v>7.115454068617387</v>
       </c>
     </row>
@@ -2816,40 +2926,45 @@
       <c r="X23">
         <v>2.25</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z23">
         <v>2.268181818181818</v>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <v>24.95</v>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <v>40.18000030517578</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>90.63999938964844</v>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <v>50.45999908447266</v>
       </c>
-      <c r="AD23">
+      <c r="AE23">
         <v>75.40999908447266</v>
       </c>
-      <c r="AE23">
+      <c r="AF23">
         <v>7.540999908447266</v>
       </c>
-      <c r="AF23">
+      <c r="AG23">
         <v>6</v>
       </c>
-      <c r="AG23">
+      <c r="AH23">
         <v>543.8399963378906</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>37.70499954223633</v>
       </c>
-      <c r="AI23">
+      <c r="AJ23">
         <v>11.34090909090909</v>
       </c>
-      <c r="AJ23">
+      <c r="AK23">
         <v>49.04590863314542</v>
       </c>
     </row>
@@ -2922,40 +3037,45 @@
       <c r="X24">
         <v>0.88</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z24">
         <v>0.8558</v>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <v>8.558</v>
       </c>
-      <c r="AA24">
+      <c r="AB24">
         <v>14.10000038146973</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>28.48999977111816</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>14.38999938964844</v>
       </c>
-      <c r="AD24">
+      <c r="AE24">
         <v>22.94799938964844</v>
       </c>
-      <c r="AE24">
+      <c r="AF24">
         <v>2.294799938964844</v>
       </c>
-      <c r="AF24">
+      <c r="AG24">
         <v>18</v>
       </c>
-      <c r="AG24">
+      <c r="AH24">
         <v>512.819995880127</v>
       </c>
-      <c r="AH24">
+      <c r="AI24">
         <v>11.47399969482422</v>
       </c>
-      <c r="AI24">
+      <c r="AJ24">
         <v>4.279</v>
       </c>
-      <c r="AJ24">
+      <c r="AK24">
         <v>15.75299969482422</v>
       </c>
     </row>
@@ -3025,40 +3145,45 @@
       <c r="W25">
         <v>1.161</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z25">
         <v>1.340444444444444</v>
       </c>
-      <c r="Z25">
+      <c r="AA25">
         <v>12.064</v>
       </c>
-      <c r="AA25">
+      <c r="AB25">
         <v>15.22999954223633</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <v>40.72999954223633</v>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <v>25.5</v>
       </c>
-      <c r="AD25">
+      <c r="AE25">
         <v>37.564</v>
       </c>
-      <c r="AE25">
+      <c r="AF25">
         <v>3.7564</v>
       </c>
-      <c r="AF25">
+      <c r="AG25">
         <v>13</v>
       </c>
-      <c r="AG25">
+      <c r="AH25">
         <v>529.4899940490723</v>
       </c>
-      <c r="AH25">
+      <c r="AI25">
         <v>18.782</v>
       </c>
-      <c r="AI25">
+      <c r="AJ25">
         <v>6.702222222222222</v>
       </c>
-      <c r="AJ25">
+      <c r="AK25">
         <v>25.48422222222222</v>
       </c>
     </row>
@@ -3134,40 +3259,45 @@
       <c r="X26">
         <v>0.4</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z26">
         <v>0.7636609090909091</v>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <v>8.400269999999999</v>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <v>20.81229782104492</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>47.61999893188477</v>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <v>26.80770111083984</v>
       </c>
-      <c r="AD26">
+      <c r="AE26">
         <v>35.20797111083984</v>
       </c>
-      <c r="AE26">
+      <c r="AF26">
         <v>3.520797111083984</v>
       </c>
-      <c r="AF26">
+      <c r="AG26">
         <v>11</v>
       </c>
-      <c r="AG26">
+      <c r="AH26">
         <v>523.8199882507324</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
         <v>17.60398555541992</v>
       </c>
-      <c r="AI26">
+      <c r="AJ26">
         <v>3.818304545454545</v>
       </c>
-      <c r="AJ26">
+      <c r="AK26">
         <v>21.42229010087447</v>
       </c>
     </row>
@@ -3243,40 +3373,45 @@
       <c r="X27">
         <v>0.205</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z27">
         <v>0.6231818181818182</v>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <v>6.855</v>
       </c>
-      <c r="AA27">
+      <c r="AB27">
         <v>18.27000045776367</v>
       </c>
-      <c r="AB27">
+      <c r="AC27">
         <v>22.10000038146973</v>
       </c>
-      <c r="AC27">
+      <c r="AD27">
         <v>3.829999923706055</v>
       </c>
-      <c r="AD27">
+      <c r="AE27">
         <v>10.68499992370606</v>
       </c>
-      <c r="AE27">
+      <c r="AF27">
         <v>1.068499992370606</v>
       </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>23</v>
       </c>
-      <c r="AG27">
+      <c r="AH27">
         <v>508.3000087738037</v>
       </c>
-      <c r="AH27">
+      <c r="AI27">
         <v>5.342499961853028</v>
       </c>
-      <c r="AI27">
+      <c r="AJ27">
         <v>3.115909090909091</v>
       </c>
-      <c r="AJ27">
+      <c r="AK27">
         <v>8.458409052762118</v>
       </c>
     </row>
@@ -3352,40 +3487,45 @@
       <c r="X28">
         <v>0.5</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z28">
         <v>1.957272727272727</v>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <v>21.53</v>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <v>41.09000015258789</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>48.72000122070313</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>7.630001068115234</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
         <v>29.16000106811524</v>
       </c>
-      <c r="AE28">
+      <c r="AF28">
         <v>2.916000106811524</v>
       </c>
-      <c r="AF28">
+      <c r="AG28">
         <v>11</v>
       </c>
-      <c r="AG28">
+      <c r="AH28">
         <v>535.9200134277344</v>
       </c>
-      <c r="AH28">
+      <c r="AI28">
         <v>14.58000053405762</v>
       </c>
-      <c r="AI28">
+      <c r="AJ28">
         <v>9.786363636363637</v>
       </c>
-      <c r="AJ28">
+      <c r="AK28">
         <v>24.36636417042126</v>
       </c>
     </row>
@@ -3461,40 +3601,45 @@
       <c r="X29">
         <v>0.9</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z29">
         <v>1.44</v>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <v>15.84</v>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <v>66.26999664306641</v>
       </c>
-      <c r="AB29">
+      <c r="AC29">
         <v>36.68999862670898</v>
       </c>
-      <c r="AC29">
+      <c r="AD29">
         <v>-29.57999801635742</v>
       </c>
-      <c r="AD29">
+      <c r="AE29">
         <v>-13.73999801635742</v>
       </c>
-      <c r="AE29">
+      <c r="AF29">
         <v>-1.373999801635742</v>
       </c>
-      <c r="AF29">
+      <c r="AG29">
         <v>14</v>
       </c>
-      <c r="AG29">
+      <c r="AH29">
         <v>513.6599807739258</v>
       </c>
-      <c r="AH29">
+      <c r="AI29">
         <v>-6.869999008178711</v>
       </c>
-      <c r="AI29">
+      <c r="AJ29">
         <v>7.199999999999999</v>
       </c>
-      <c r="AJ29">
+      <c r="AK29">
         <v>0.3300009918212883</v>
       </c>
     </row>
@@ -3570,40 +3715,45 @@
       <c r="X30">
         <v>1.34</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z30">
         <v>2.883181818181818</v>
       </c>
-      <c r="Z30">
+      <c r="AA30">
         <v>31.715</v>
       </c>
-      <c r="AA30">
+      <c r="AB30">
         <v>36.77000045776367</v>
       </c>
-      <c r="AB30">
+      <c r="AC30">
         <v>54.04999923706055</v>
       </c>
-      <c r="AC30">
+      <c r="AD30">
         <v>17.27999877929688</v>
       </c>
-      <c r="AD30">
+      <c r="AE30">
         <v>48.99499877929688</v>
       </c>
-      <c r="AE30">
+      <c r="AF30">
         <v>4.899499877929688</v>
       </c>
-      <c r="AF30">
+      <c r="AG30">
         <v>10</v>
       </c>
-      <c r="AG30">
+      <c r="AH30">
         <v>540.4999923706055</v>
       </c>
-      <c r="AH30">
+      <c r="AI30">
         <v>24.49749938964844</v>
       </c>
-      <c r="AI30">
+      <c r="AJ30">
         <v>14.41590909090909</v>
       </c>
-      <c r="AJ30">
+      <c r="AK30">
         <v>38.91340848055753</v>
       </c>
     </row>
@@ -3679,40 +3829,45 @@
       <c r="X31">
         <v>0.65</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z31">
         <v>3.109363636363637</v>
       </c>
-      <c r="Z31">
+      <c r="AA31">
         <v>34.203</v>
       </c>
-      <c r="AA31">
+      <c r="AB31">
         <v>33.90000152587891</v>
       </c>
-      <c r="AB31">
+      <c r="AC31">
         <v>68.73999786376953</v>
       </c>
-      <c r="AC31">
+      <c r="AD31">
         <v>34.83999633789063</v>
       </c>
-      <c r="AD31">
+      <c r="AE31">
         <v>69.04299633789063</v>
       </c>
-      <c r="AE31">
+      <c r="AF31">
         <v>6.904299633789063</v>
       </c>
-      <c r="AF31">
+      <c r="AG31">
         <v>8</v>
       </c>
-      <c r="AG31">
+      <c r="AH31">
         <v>549.9199829101563</v>
       </c>
-      <c r="AH31">
+      <c r="AI31">
         <v>34.52149816894531</v>
       </c>
-      <c r="AI31">
+      <c r="AJ31">
         <v>15.54681818181818</v>
       </c>
-      <c r="AJ31">
+      <c r="AK31">
         <v>50.0683163507635</v>
       </c>
     </row>
@@ -3788,40 +3943,45 @@
       <c r="X32">
         <v>0.354</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z32">
         <v>0.7749090909090909</v>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <v>8.523999999999999</v>
       </c>
-      <c r="AA32">
+      <c r="AB32">
         <v>17.81999969482422</v>
       </c>
-      <c r="AB32">
+      <c r="AC32">
         <v>38.22999954223633</v>
       </c>
-      <c r="AC32">
+      <c r="AD32">
         <v>20.40999984741211</v>
       </c>
-      <c r="AD32">
+      <c r="AE32">
         <v>28.93399984741211</v>
       </c>
-      <c r="AE32">
+      <c r="AF32">
         <v>2.893399984741211</v>
       </c>
-      <c r="AF32">
+      <c r="AG32">
         <v>14</v>
       </c>
-      <c r="AG32">
+      <c r="AH32">
         <v>535.2199935913086</v>
       </c>
-      <c r="AH32">
+      <c r="AI32">
         <v>14.46699992370606</v>
       </c>
-      <c r="AI32">
+      <c r="AJ32">
         <v>3.874545454545455</v>
       </c>
-      <c r="AJ32">
+      <c r="AK32">
         <v>18.34154537825151</v>
       </c>
     </row>
@@ -3897,40 +4057,45 @@
       <c r="X33">
         <v>0.7</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z33">
         <v>3.343636363636364</v>
       </c>
-      <c r="Z33">
+      <c r="AA33">
         <v>36.78</v>
       </c>
-      <c r="AA33">
+      <c r="AB33">
         <v>39.88000106811523</v>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <v>22.60000038146973</v>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <v>-17.28000068664551</v>
       </c>
-      <c r="AD33">
+      <c r="AE33">
         <v>19.49999931335449</v>
       </c>
-      <c r="AE33">
+      <c r="AF33">
         <v>1.949999931335449</v>
       </c>
-      <c r="AF33">
+      <c r="AG33">
         <v>23</v>
       </c>
-      <c r="AG33">
+      <c r="AH33">
         <v>519.8000087738037</v>
       </c>
-      <c r="AH33">
+      <c r="AI33">
         <v>9.749999656677247</v>
       </c>
-      <c r="AI33">
+      <c r="AJ33">
         <v>16.71818181818182</v>
       </c>
-      <c r="AJ33">
+      <c r="AK33">
         <v>26.46818147485907</v>
       </c>
     </row>
@@ -4000,40 +4165,45 @@
       <c r="X34">
         <v>0.621</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z34">
         <v>0.4551158888888889</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>4.096043</v>
       </c>
-      <c r="AA34">
+      <c r="AB34">
         <v>5.959052085876465</v>
       </c>
-      <c r="AB34">
+      <c r="AC34">
         <v>16.11000061035156</v>
       </c>
-      <c r="AC34">
+      <c r="AD34">
         <v>10.1509485244751</v>
       </c>
-      <c r="AD34">
+      <c r="AE34">
         <v>14.2469915244751</v>
       </c>
-      <c r="AE34">
+      <c r="AF34">
         <v>1.42469915244751</v>
       </c>
-      <c r="AF34">
+      <c r="AG34">
         <v>32</v>
       </c>
-      <c r="AG34">
+      <c r="AH34">
         <v>515.52001953125</v>
       </c>
-      <c r="AH34">
+      <c r="AI34">
         <v>7.123495762237548</v>
       </c>
-      <c r="AI34">
+      <c r="AJ34">
         <v>2.275579444444444</v>
       </c>
-      <c r="AJ34">
+      <c r="AK34">
         <v>9.399075206681992</v>
       </c>
     </row>
@@ -4100,40 +4270,45 @@
       <c r="X35">
         <v>1.05</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z35">
         <v>4.45375</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>35.63</v>
       </c>
-      <c r="AA35">
+      <c r="AB35">
         <v>22.13999938964844</v>
       </c>
-      <c r="AB35">
+      <c r="AC35">
         <v>58.90999984741211</v>
       </c>
-      <c r="AC35">
+      <c r="AD35">
         <v>36.77000045776367</v>
       </c>
-      <c r="AD35">
+      <c r="AE35">
         <v>72.40000045776367</v>
       </c>
-      <c r="AE35">
+      <c r="AF35">
         <v>7.240000045776367</v>
       </c>
-      <c r="AF35">
+      <c r="AG35">
         <v>9</v>
       </c>
-      <c r="AG35">
+      <c r="AH35">
         <v>530.189998626709</v>
       </c>
-      <c r="AH35">
+      <c r="AI35">
         <v>36.20000022888183</v>
       </c>
-      <c r="AI35">
+      <c r="AJ35">
         <v>22.26875</v>
       </c>
-      <c r="AJ35">
+      <c r="AK35">
         <v>58.46875022888183</v>
       </c>
     </row>
@@ -4209,40 +4384,45 @@
       <c r="X36">
         <v>0.9299999999999999</v>
       </c>
-      <c r="Y36">
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z36">
         <v>1.082818181818182</v>
       </c>
-      <c r="Z36">
+      <c r="AA36">
         <v>11.911</v>
       </c>
-      <c r="AA36">
+      <c r="AB36">
         <v>52.59000015258789</v>
       </c>
-      <c r="AB36">
+      <c r="AC36">
         <v>48.52000045776367</v>
       </c>
-      <c r="AC36">
+      <c r="AD36">
         <v>-4.069999694824219</v>
       </c>
-      <c r="AD36">
+      <c r="AE36">
         <v>7.841000305175781</v>
       </c>
-      <c r="AE36">
+      <c r="AF36">
         <v>0.784100030517578</v>
       </c>
-      <c r="AF36">
+      <c r="AG36">
         <v>11</v>
       </c>
-      <c r="AG36">
+      <c r="AH36">
         <v>533.7200050354004</v>
       </c>
-      <c r="AH36">
+      <c r="AI36">
         <v>3.92050015258789</v>
       </c>
-      <c r="AI36">
+      <c r="AJ36">
         <v>5.414090909090909</v>
       </c>
-      <c r="AJ36">
+      <c r="AK36">
         <v>9.3345910616788</v>
       </c>
     </row>
@@ -4318,40 +4498,45 @@
       <c r="X37">
         <v>1.4</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z37">
         <v>3.954545454545455</v>
       </c>
-      <c r="Z37">
+      <c r="AA37">
         <v>43.5</v>
       </c>
-      <c r="AA37">
+      <c r="AB37">
         <v>104.0599975585938</v>
       </c>
-      <c r="AB37">
+      <c r="AC37">
         <v>96.44999694824219</v>
       </c>
-      <c r="AC37">
+      <c r="AD37">
         <v>-7.610000610351563</v>
       </c>
-      <c r="AD37">
+      <c r="AE37">
         <v>35.88999938964844</v>
       </c>
-      <c r="AE37">
+      <c r="AF37">
         <v>3.588999938964844</v>
       </c>
-      <c r="AF37">
+      <c r="AG37">
         <v>6</v>
       </c>
-      <c r="AG37">
+      <c r="AH37">
         <v>578.6999816894531</v>
       </c>
-      <c r="AH37">
+      <c r="AI37">
         <v>17.94499969482422</v>
       </c>
-      <c r="AI37">
+      <c r="AJ37">
         <v>19.77272727272727</v>
       </c>
-      <c r="AJ37">
+      <c r="AK37">
         <v>37.71772696755149</v>
       </c>
     </row>
@@ -4427,40 +4612,45 @@
       <c r="X38">
         <v>0.265</v>
       </c>
-      <c r="Y38">
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z38">
         <v>0.6113636363636363</v>
       </c>
-      <c r="Z38">
+      <c r="AA38">
         <v>6.725000000000001</v>
       </c>
-      <c r="AA38">
+      <c r="AB38">
         <v>14.35999965667725</v>
       </c>
-      <c r="AB38">
+      <c r="AC38">
         <v>28.35000038146973</v>
       </c>
-      <c r="AC38">
+      <c r="AD38">
         <v>13.99000072479248</v>
       </c>
-      <c r="AD38">
+      <c r="AE38">
         <v>20.71500072479248</v>
       </c>
-      <c r="AE38">
+      <c r="AF38">
         <v>2.071500072479248</v>
       </c>
-      <c r="AF38">
+      <c r="AG38">
         <v>18</v>
       </c>
-      <c r="AG38">
+      <c r="AH38">
         <v>510.3000068664551</v>
       </c>
-      <c r="AH38">
+      <c r="AI38">
         <v>10.35750036239624</v>
       </c>
-      <c r="AI38">
+      <c r="AJ38">
         <v>3.056818181818182</v>
       </c>
-      <c r="AJ38">
+      <c r="AK38">
         <v>13.41431854421442</v>
       </c>
     </row>
@@ -4536,40 +4726,45 @@
       <c r="X39">
         <v>0.672</v>
       </c>
-      <c r="Y39">
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z39">
         <v>1.554090909090909</v>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <v>17.095</v>
       </c>
-      <c r="AA39">
+      <c r="AB39">
         <v>38.40999984741211</v>
       </c>
-      <c r="AB39">
+      <c r="AC39">
         <v>70.31999969482422</v>
       </c>
-      <c r="AC39">
+      <c r="AD39">
         <v>31.90999984741211</v>
       </c>
-      <c r="AD39">
+      <c r="AE39">
         <v>49.00499984741211</v>
       </c>
-      <c r="AE39">
+      <c r="AF39">
         <v>4.900499984741211</v>
       </c>
-      <c r="AF39">
+      <c r="AG39">
         <v>8</v>
       </c>
-      <c r="AG39">
+      <c r="AH39">
         <v>562.5599975585938</v>
       </c>
-      <c r="AH39">
+      <c r="AI39">
         <v>24.50249992370605</v>
       </c>
-      <c r="AI39">
+      <c r="AJ39">
         <v>7.770454545454545</v>
       </c>
-      <c r="AJ39">
+      <c r="AK39">
         <v>32.2729544691606</v>
       </c>
     </row>
@@ -4642,40 +4837,45 @@
       <c r="X40">
         <v>2</v>
       </c>
-      <c r="Y40">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z40">
         <v>1.5439</v>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <v>15.439</v>
       </c>
-      <c r="AA40">
+      <c r="AB40">
         <v>23.76000022888184</v>
       </c>
-      <c r="AB40">
+      <c r="AC40">
         <v>42.16999816894531</v>
       </c>
-      <c r="AC40">
+      <c r="AD40">
         <v>18.40999794006348</v>
       </c>
-      <c r="AD40">
+      <c r="AE40">
         <v>33.84899794006348</v>
       </c>
-      <c r="AE40">
+      <c r="AF40">
         <v>3.384899794006348</v>
       </c>
-      <c r="AF40">
+      <c r="AG40">
         <v>12</v>
       </c>
-      <c r="AG40">
+      <c r="AH40">
         <v>506.0399780273438</v>
       </c>
-      <c r="AH40">
+      <c r="AI40">
         <v>16.92449897003174</v>
       </c>
-      <c r="AI40">
+      <c r="AJ40">
         <v>7.7195</v>
       </c>
-      <c r="AJ40">
+      <c r="AK40">
         <v>24.64399897003174</v>
       </c>
     </row>
@@ -4751,40 +4951,45 @@
       <c r="X41">
         <v>0.48</v>
       </c>
-      <c r="Y41">
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z41">
         <v>1.745454545454545</v>
       </c>
-      <c r="Z41">
+      <c r="AA41">
         <v>19.2</v>
       </c>
-      <c r="AA41">
+      <c r="AB41">
         <v>21.95000076293945</v>
       </c>
-      <c r="AB41">
+      <c r="AC41">
         <v>18.23999977111816</v>
       </c>
-      <c r="AC41">
+      <c r="AD41">
         <v>-3.710000991821289</v>
       </c>
-      <c r="AD41">
+      <c r="AE41">
         <v>15.48999900817871</v>
       </c>
-      <c r="AE41">
+      <c r="AF41">
         <v>1.548999900817871</v>
       </c>
-      <c r="AF41">
+      <c r="AG41">
         <v>28</v>
       </c>
-      <c r="AG41">
+      <c r="AH41">
         <v>510.7199935913086</v>
       </c>
-      <c r="AH41">
+      <c r="AI41">
         <v>7.744999504089355</v>
       </c>
-      <c r="AI41">
+      <c r="AJ41">
         <v>8.727272727272727</v>
       </c>
-      <c r="AJ41">
+      <c r="AK41">
         <v>16.47227223136208</v>
       </c>
     </row>
@@ -4857,40 +5062,45 @@
       <c r="X42">
         <v>3.291</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z42">
         <v>1.6139</v>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <v>16.139</v>
       </c>
-      <c r="AA42">
+      <c r="AB42">
         <v>24.14999961853027</v>
       </c>
-      <c r="AB42">
+      <c r="AC42">
         <v>35.5099983215332</v>
       </c>
-      <c r="AC42">
+      <c r="AD42">
         <v>11.35999870300293</v>
       </c>
-      <c r="AD42">
+      <c r="AE42">
         <v>27.49899870300293</v>
       </c>
-      <c r="AE42">
+      <c r="AF42">
         <v>2.749899870300293</v>
       </c>
-      <c r="AF42">
+      <c r="AG42">
         <v>15</v>
       </c>
-      <c r="AG42">
+      <c r="AH42">
         <v>532.649974822998</v>
       </c>
-      <c r="AH42">
+      <c r="AI42">
         <v>13.74949935150146</v>
       </c>
-      <c r="AI42">
+      <c r="AJ42">
         <v>8.069500000000001</v>
       </c>
-      <c r="AJ42">
+      <c r="AK42">
         <v>21.81899935150147</v>
       </c>
     </row>
@@ -4966,40 +5176,45 @@
       <c r="X43">
         <v>0.52</v>
       </c>
-      <c r="Y43">
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z43">
         <v>1.620909090909091</v>
       </c>
-      <c r="Z43">
+      <c r="AA43">
         <v>17.83</v>
       </c>
-      <c r="AA43">
+      <c r="AB43">
         <v>47.02000045776367</v>
       </c>
-      <c r="AB43">
+      <c r="AC43">
         <v>51.06999969482422</v>
       </c>
-      <c r="AC43">
+      <c r="AD43">
         <v>4.049999237060547</v>
       </c>
-      <c r="AD43">
+      <c r="AE43">
         <v>21.87999923706055</v>
       </c>
-      <c r="AE43">
+      <c r="AF43">
         <v>2.187999923706055</v>
       </c>
-      <c r="AF43">
+      <c r="AG43">
         <v>10</v>
       </c>
-      <c r="AG43">
+      <c r="AH43">
         <v>510.6999969482422</v>
       </c>
-      <c r="AH43">
+      <c r="AI43">
         <v>10.93999961853027</v>
       </c>
-      <c r="AI43">
+      <c r="AJ43">
         <v>8.104545454545454</v>
       </c>
-      <c r="AJ43">
+      <c r="AK43">
         <v>19.04454507307573</v>
       </c>
     </row>
@@ -5075,40 +5290,45 @@
       <c r="X44">
         <v>1.3</v>
       </c>
-      <c r="Y44">
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z44">
         <v>3.789090909090909</v>
       </c>
-      <c r="Z44">
+      <c r="AA44">
         <v>41.68</v>
       </c>
-      <c r="AA44">
+      <c r="AB44">
         <v>75.26000213623047</v>
       </c>
-      <c r="AB44">
+      <c r="AC44">
         <v>99.13999938964844</v>
       </c>
-      <c r="AC44">
+      <c r="AD44">
         <v>23.87999725341797</v>
       </c>
-      <c r="AD44">
+      <c r="AE44">
         <v>65.55999725341798</v>
       </c>
-      <c r="AE44">
+      <c r="AF44">
         <v>6.555999725341797</v>
       </c>
-      <c r="AF44">
+      <c r="AG44">
         <v>6</v>
       </c>
-      <c r="AG44">
+      <c r="AH44">
         <v>594.8399963378906</v>
       </c>
-      <c r="AH44">
+      <c r="AI44">
         <v>32.77999862670899</v>
       </c>
-      <c r="AI44">
+      <c r="AJ44">
         <v>18.94545454545455</v>
       </c>
-      <c r="AJ44">
+      <c r="AK44">
         <v>51.72545317216353</v>
       </c>
     </row>
@@ -5181,40 +5401,45 @@
       <c r="W45">
         <v>2.18</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z45">
         <v>1.8141</v>
       </c>
-      <c r="Z45">
+      <c r="AA45">
         <v>18.141</v>
       </c>
-      <c r="AA45">
+      <c r="AB45">
         <v>28.13999938964844</v>
       </c>
-      <c r="AB45">
+      <c r="AC45">
         <v>57.18000030517578</v>
       </c>
-      <c r="AC45">
+      <c r="AD45">
         <v>29.04000091552734</v>
       </c>
-      <c r="AD45">
+      <c r="AE45">
         <v>47.18100091552734</v>
       </c>
-      <c r="AE45">
+      <c r="AF45">
         <v>4.718100091552734</v>
       </c>
-      <c r="AF45">
+      <c r="AG45">
         <v>9</v>
       </c>
-      <c r="AG45">
+      <c r="AH45">
         <v>514.620002746582</v>
       </c>
-      <c r="AH45">
+      <c r="AI45">
         <v>23.59050045776367</v>
       </c>
-      <c r="AI45">
+      <c r="AJ45">
         <v>9.070499999999999</v>
       </c>
-      <c r="AJ45">
+      <c r="AK45">
         <v>32.66100045776367</v>
       </c>
     </row>
@@ -5290,40 +5515,45 @@
       <c r="X46">
         <v>0.52</v>
       </c>
-      <c r="Y46">
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z46">
         <v>1.516818181818182</v>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <v>16.685</v>
       </c>
-      <c r="AA46">
+      <c r="AB46">
         <v>51.36999893188477</v>
       </c>
-      <c r="AB46">
+      <c r="AC46">
         <v>56.84000015258789</v>
       </c>
-      <c r="AC46">
+      <c r="AD46">
         <v>5.470001220703125</v>
       </c>
-      <c r="AD46">
+      <c r="AE46">
         <v>22.15500122070312</v>
       </c>
-      <c r="AE46">
+      <c r="AF46">
         <v>2.215500122070313</v>
       </c>
-      <c r="AF46">
+      <c r="AG46">
         <v>9</v>
       </c>
-      <c r="AG46">
+      <c r="AH46">
         <v>511.560001373291</v>
       </c>
-      <c r="AH46">
+      <c r="AI46">
         <v>11.07750061035156</v>
       </c>
-      <c r="AI46">
+      <c r="AJ46">
         <v>7.584090909090909</v>
       </c>
-      <c r="AJ46">
+      <c r="AK46">
         <v>18.66159151944247</v>
       </c>
     </row>
@@ -5378,40 +5608,45 @@
       <c r="W47">
         <v>2.257</v>
       </c>
-      <c r="Y47">
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z47">
         <v>2.34775</v>
       </c>
-      <c r="Z47">
+      <c r="AA47">
         <v>9.391</v>
       </c>
-      <c r="AA47">
+      <c r="AB47">
         <v>32</v>
       </c>
-      <c r="AB47">
+      <c r="AC47">
         <v>71.59999847412109</v>
       </c>
-      <c r="AC47">
+      <c r="AD47">
         <v>39.59999847412109</v>
       </c>
-      <c r="AD47">
+      <c r="AE47">
         <v>48.99099847412109</v>
       </c>
-      <c r="AE47">
+      <c r="AF47">
         <v>4.899099847412109</v>
       </c>
-      <c r="AF47">
+      <c r="AG47">
         <v>7</v>
       </c>
-      <c r="AG47">
+      <c r="AH47">
         <v>501.1999893188477</v>
       </c>
-      <c r="AH47">
+      <c r="AI47">
         <v>24.49549923706055</v>
       </c>
-      <c r="AI47">
+      <c r="AJ47">
         <v>11.73875</v>
       </c>
-      <c r="AJ47">
+      <c r="AK47">
         <v>36.23424923706055</v>
       </c>
     </row>

--- a/ProductionBuild/fullviewhealth.result.xlsx
+++ b/ProductionBuild/fullviewhealth.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -422,52 +422,52 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Div_2024</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Div_2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Div_2016</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Div_2017</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Div_2018</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Div_2019</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Div_2020</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Div_2021</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Div_2022</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Div_2023</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Div_2024</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Div_2025</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
@@ -549,79 +549,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="C2">
-        <v>17.93000030517578</v>
+        <v>38.5099983215332</v>
       </c>
       <c r="D2">
-        <v>26.83499908447266</v>
+        <v>35.47000122070313</v>
       </c>
       <c r="E2">
-        <v>23.03499984741211</v>
+        <v>38.20999908447266</v>
       </c>
       <c r="F2">
-        <v>28.94000053405762</v>
+        <v>46.9900016784668</v>
       </c>
       <c r="G2">
-        <v>34.92499923706055</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>44.09999847412109</v>
       </c>
       <c r="I2">
-        <v>67.66999816894531</v>
+        <v>35.13999938964844</v>
       </c>
       <c r="J2">
-        <v>103.4499969482422</v>
+        <v>37.06000137329102</v>
       </c>
       <c r="K2">
-        <v>86.01999664306641</v>
+        <v>33.81999969482422</v>
       </c>
       <c r="L2">
-        <v>50.88000106811523</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="M2">
-        <v>39.15000152587891</v>
+        <v>55.63000106811523</v>
       </c>
       <c r="N2">
-        <v>0.2235</v>
+        <v>1.557</v>
       </c>
       <c r="O2">
-        <v>0.5685</v>
+        <v>1.675</v>
       </c>
       <c r="P2">
-        <v>0.5685</v>
+        <v>1.517</v>
       </c>
       <c r="Q2">
-        <v>0.619</v>
+        <v>2.064</v>
       </c>
       <c r="R2">
-        <v>0.6525000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="S2">
-        <v>0.753</v>
+        <v>2.045</v>
       </c>
       <c r="T2">
-        <v>0.8100000000000001</v>
+        <v>2.058</v>
       </c>
       <c r="U2">
-        <v>1.0365</v>
+        <v>2.208</v>
       </c>
       <c r="V2">
-        <v>1.443</v>
+        <v>1.68</v>
       </c>
       <c r="W2">
-        <v>1.683</v>
+        <v>1.389</v>
       </c>
       <c r="X2">
-        <v>1.275</v>
+        <v>0.486</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -629,40 +629,40 @@
         </is>
       </c>
       <c r="Z2">
-        <v>0.8756818181818182</v>
+        <v>1.712636363636364</v>
       </c>
       <c r="AA2">
-        <v>9.6325</v>
+        <v>18.839</v>
       </c>
       <c r="AB2">
-        <v>17.93000030517578</v>
+        <v>38.5099983215332</v>
       </c>
       <c r="AC2">
-        <v>39.15000152587891</v>
+        <v>55.63000106811523</v>
       </c>
       <c r="AD2">
-        <v>21.22000122070313</v>
+        <v>17.12000274658203</v>
       </c>
       <c r="AE2">
-        <v>30.85250122070313</v>
+        <v>35.95900274658203</v>
       </c>
       <c r="AF2">
-        <v>3.085250122070312</v>
+        <v>3.595900274658203</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AH2">
-        <v>508.9500198364258</v>
+        <v>500.6700096130371</v>
       </c>
       <c r="AI2">
-        <v>15.42625061035156</v>
+        <v>17.97950137329101</v>
       </c>
       <c r="AJ2">
-        <v>4.378409090909091</v>
+        <v>8.563181818181819</v>
       </c>
       <c r="AK2">
-        <v>19.80465970126065</v>
+        <v>26.54268319147283</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -673,76 +673,76 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sanofi</t>
+          <t>Roche Holding AG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>RHHBY</t>
         </is>
       </c>
       <c r="C3">
-        <v>40.43999862670898</v>
+        <v>28.53000068664551</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>31.57999992370605</v>
       </c>
       <c r="E3">
-        <v>43.40999984741211</v>
+        <v>31.07999992370605</v>
       </c>
       <c r="F3">
-        <v>50.20000076293945</v>
+        <v>40.65999984741211</v>
       </c>
       <c r="G3">
-        <v>48.59000015258789</v>
+        <v>43.84000015258789</v>
       </c>
       <c r="H3">
-        <v>50.09999847412109</v>
+        <v>51.68999862670898</v>
       </c>
       <c r="I3">
-        <v>48.43000030517578</v>
+        <v>39.15000152587891</v>
       </c>
       <c r="J3">
-        <v>49.72999954223633</v>
+        <v>36.22999954223633</v>
       </c>
       <c r="K3">
-        <v>48.22999954223633</v>
+        <v>34.88000106811523</v>
       </c>
       <c r="L3">
-        <v>48.45999908447266</v>
+        <v>51.56999969482422</v>
       </c>
       <c r="M3">
-        <v>46.90000152587891</v>
+        <v>51.86000061035156</v>
       </c>
       <c r="N3">
-        <v>1.63</v>
+        <v>1.393</v>
       </c>
       <c r="O3">
-        <v>1.577</v>
-      </c>
-      <c r="P3">
-        <v>1.861</v>
+        <v>1.363</v>
       </c>
       <c r="Q3">
-        <v>1.739</v>
+        <v>1.018</v>
       </c>
       <c r="R3">
-        <v>1.753</v>
+        <v>1.113</v>
       </c>
       <c r="S3">
-        <v>1.906</v>
+        <v>1.094</v>
       </c>
       <c r="T3">
-        <v>2.044</v>
+        <v>1.151</v>
       </c>
       <c r="U3">
-        <v>1.903</v>
+        <v>1.278</v>
       </c>
       <c r="V3">
-        <v>2.037</v>
+        <v>1.265</v>
       </c>
       <c r="W3">
-        <v>2.212</v>
+        <v>1.287</v>
+      </c>
+      <c r="X3">
+        <v>1.593</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -750,40 +750,40 @@
         </is>
       </c>
       <c r="Z3">
-        <v>1.8662</v>
+        <v>1.2555</v>
       </c>
       <c r="AA3">
-        <v>18.662</v>
+        <v>12.555</v>
       </c>
       <c r="AB3">
-        <v>40.43999862670898</v>
+        <v>28.53000068664551</v>
       </c>
       <c r="AC3">
-        <v>46.90000152587891</v>
+        <v>51.86000061035156</v>
       </c>
       <c r="AD3">
-        <v>6.460002899169922</v>
+        <v>23.32999992370605</v>
       </c>
       <c r="AE3">
-        <v>25.12200289916992</v>
+        <v>35.88499992370605</v>
       </c>
       <c r="AF3">
-        <v>2.512200289916992</v>
+        <v>3.588499992370605</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>515.900016784668</v>
+        <v>518.6000061035156</v>
       </c>
       <c r="AI3">
-        <v>12.56100144958496</v>
+        <v>17.94249996185303</v>
       </c>
       <c r="AJ3">
-        <v>9.331</v>
+        <v>6.2775</v>
       </c>
       <c r="AK3">
-        <v>21.89200144958496</v>
+        <v>24.21999996185303</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -794,79 +794,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Medtronic PLC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="C4">
-        <v>58.43999862670898</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="D4">
-        <v>61.27999877929688</v>
+        <v>80.75</v>
       </c>
       <c r="E4">
-        <v>51.97999954223633</v>
+        <v>90.95999908447266</v>
       </c>
       <c r="F4">
-        <v>64.19000244140625</v>
+        <v>113.4499969482422</v>
       </c>
       <c r="G4">
-        <v>62.02999877929688</v>
+        <v>117.1399993896484</v>
       </c>
       <c r="H4">
-        <v>62.34999847412109</v>
+        <v>103.4499969482422</v>
       </c>
       <c r="I4">
-        <v>71.94999694824219</v>
+        <v>77.72000122070313</v>
       </c>
       <c r="J4">
-        <v>51.31000137329102</v>
+        <v>82.37999725341797</v>
       </c>
       <c r="K4">
-        <v>56.56000137329102</v>
+        <v>79.87999725341797</v>
       </c>
       <c r="L4">
-        <v>53.93999862670898</v>
+        <v>96.05999755859375</v>
       </c>
       <c r="M4">
-        <v>58.79999923706055</v>
+        <v>83.79000091552734</v>
       </c>
       <c r="N4">
-        <v>0.76</v>
+        <v>2.79</v>
       </c>
       <c r="O4">
-        <v>1.56</v>
+        <v>2.83</v>
       </c>
       <c r="P4">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="R4">
-        <v>2.29</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="T4">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="V4">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="W4">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="X4">
-        <v>1.26</v>
+        <v>0.71</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -874,40 +874,40 @@
         </is>
       </c>
       <c r="Z4">
-        <v>1.809090909090909</v>
+        <v>2.107272727272727</v>
       </c>
       <c r="AA4">
-        <v>19.9</v>
+        <v>23.18</v>
       </c>
       <c r="AB4">
-        <v>58.43999862670898</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="AC4">
-        <v>58.79999923706055</v>
+        <v>83.79000091552734</v>
       </c>
       <c r="AD4">
-        <v>0.3600006103515625</v>
+        <v>12.55999755859375</v>
       </c>
       <c r="AE4">
-        <v>20.26000061035156</v>
+        <v>35.73999755859375</v>
       </c>
       <c r="AF4">
-        <v>2.026000061035156</v>
+        <v>3.573999755859375</v>
       </c>
       <c r="AG4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AH4">
-        <v>529.1999931335449</v>
+        <v>502.7400054931641</v>
       </c>
       <c r="AI4">
-        <v>10.13000030517578</v>
+        <v>17.86999877929687</v>
       </c>
       <c r="AJ4">
-        <v>9.045454545454545</v>
+        <v>10.53636363636364</v>
       </c>
       <c r="AK4">
-        <v>19.17545485063032</v>
+        <v>28.40636241566051</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -918,79 +918,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer Inc</t>
+          <t>Novo Nordisk A/S</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="C5">
-        <v>30.81593894958496</v>
+        <v>17.93000030517578</v>
       </c>
       <c r="D5">
-        <v>34.36432647705078</v>
+        <v>26.83499908447266</v>
       </c>
       <c r="E5">
-        <v>41.41366195678711</v>
+        <v>23.03499984741211</v>
       </c>
       <c r="F5">
-        <v>37.17267608642578</v>
+        <v>28.94000053405762</v>
       </c>
       <c r="G5">
-        <v>36.81000137329102</v>
+        <v>34.92499923706055</v>
       </c>
       <c r="H5">
-        <v>59.04999923706055</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>51.2400016784668</v>
+        <v>67.66999816894531</v>
       </c>
       <c r="J5">
-        <v>28.79000091552734</v>
+        <v>103.4499969482422</v>
       </c>
       <c r="K5">
-        <v>26.53000068664551</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="L5">
-        <v>24.89999961853027</v>
+        <v>50.88000106811523</v>
       </c>
       <c r="M5">
-        <v>26.79999923706055</v>
+        <v>38.52000045776367</v>
       </c>
       <c r="N5">
-        <v>0.85389</v>
+        <v>1.443</v>
       </c>
       <c r="O5">
-        <v>1.21442</v>
+        <v>1.683</v>
       </c>
       <c r="P5">
-        <v>1.290324</v>
+        <v>0.2235</v>
       </c>
       <c r="Q5">
-        <v>1.366224</v>
+        <v>0.5685</v>
       </c>
       <c r="R5">
-        <v>1.442124</v>
+        <v>0.5685</v>
       </c>
       <c r="S5">
-        <v>1.56</v>
+        <v>0.619</v>
       </c>
       <c r="T5">
-        <v>1.6</v>
+        <v>0.6525000000000001</v>
       </c>
       <c r="U5">
-        <v>1.64</v>
+        <v>0.753</v>
       </c>
       <c r="V5">
-        <v>1.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.0365</v>
       </c>
       <c r="X5">
-        <v>0.43</v>
+        <v>1.275</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -998,40 +998,40 @@
         </is>
       </c>
       <c r="Z5">
-        <v>1.345180181818182</v>
+        <v>0.8756818181818182</v>
       </c>
       <c r="AA5">
-        <v>14.796982</v>
+        <v>9.6325</v>
       </c>
       <c r="AB5">
-        <v>30.81593894958496</v>
+        <v>17.93000030517578</v>
       </c>
       <c r="AC5">
-        <v>26.79999923706055</v>
+        <v>38.52000045776367</v>
       </c>
       <c r="AD5">
-        <v>-4.015939712524414</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="AE5">
-        <v>10.78104228747559</v>
+        <v>30.22250015258789</v>
       </c>
       <c r="AF5">
-        <v>1.078104228747559</v>
+        <v>3.022250015258789</v>
       </c>
       <c r="AG5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>509.1999855041504</v>
+        <v>500.7600059509277</v>
       </c>
       <c r="AI5">
-        <v>5.390521143737793</v>
+        <v>15.11125007629395</v>
       </c>
       <c r="AJ5">
-        <v>6.725900909090909</v>
+        <v>4.378409090909091</v>
       </c>
       <c r="AK5">
-        <v>12.1164220528287</v>
+        <v>19.48965916720304</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1042,79 +1042,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sonic Healthcare Ltd</t>
+          <t>Sonova Holding AG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKHHY</t>
+          <t>SONVY</t>
         </is>
       </c>
       <c r="C6">
-        <v>15.35999965667725</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="D6">
-        <v>17.85000038146973</v>
+        <v>31.25</v>
       </c>
       <c r="E6">
-        <v>15.75</v>
+        <v>32.77999877929688</v>
       </c>
       <c r="F6">
-        <v>20.23999977111816</v>
+        <v>45.7599983215332</v>
       </c>
       <c r="G6">
-        <v>24.55999946594238</v>
+        <v>52.52999877929688</v>
       </c>
       <c r="H6">
-        <v>33.63999938964844</v>
+        <v>78.51999664306641</v>
       </c>
       <c r="I6">
-        <v>20.38999938964844</v>
+        <v>47.31999969482422</v>
       </c>
       <c r="J6">
-        <v>21.75</v>
+        <v>65.33000183105469</v>
       </c>
       <c r="K6">
-        <v>16.68000030517578</v>
+        <v>65.04000091552734</v>
       </c>
       <c r="L6">
-        <v>15.10000038146973</v>
+        <v>51.68999862670898</v>
       </c>
       <c r="M6">
-        <v>14.3100004196167</v>
+        <v>44.29000091552734</v>
       </c>
       <c r="N6">
-        <v>0.336</v>
+        <v>0.952</v>
       </c>
       <c r="O6">
-        <v>0.604</v>
+        <v>1.077</v>
       </c>
       <c r="P6">
-        <v>0.254</v>
+        <v>0.458</v>
       </c>
       <c r="Q6">
-        <v>0.579</v>
+        <v>0.478</v>
       </c>
       <c r="R6">
-        <v>0.59</v>
+        <v>0.526</v>
       </c>
       <c r="S6">
-        <v>0.678</v>
-      </c>
-      <c r="T6">
-        <v>0.705</v>
+        <v>0.575</v>
       </c>
       <c r="U6">
-        <v>0.6850000000000001</v>
+        <v>0.712</v>
       </c>
       <c r="V6">
-        <v>0.709</v>
+        <v>0.917</v>
       </c>
       <c r="W6">
-        <v>0.276</v>
-      </c>
-      <c r="X6">
-        <v>0.318</v>
+        <v>1.024</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1122,40 +1116,40 @@
         </is>
       </c>
       <c r="Z6">
-        <v>0.5212727272727272</v>
+        <v>0.7465555555555555</v>
       </c>
       <c r="AA6">
-        <v>5.734</v>
+        <v>6.719</v>
       </c>
       <c r="AB6">
-        <v>15.35999965667725</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="AC6">
-        <v>14.3100004196167</v>
+        <v>44.29000091552734</v>
       </c>
       <c r="AD6">
-        <v>-1.049999237060547</v>
+        <v>20.18000030517578</v>
       </c>
       <c r="AE6">
-        <v>4.684000762939453</v>
+        <v>26.89900030517578</v>
       </c>
       <c r="AF6">
-        <v>0.4684000762939453</v>
+        <v>2.689900030517578</v>
       </c>
       <c r="AG6">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="AH6">
-        <v>500.8500146865845</v>
+        <v>531.4800109863281</v>
       </c>
       <c r="AI6">
-        <v>2.342000381469727</v>
+        <v>13.44950015258789</v>
       </c>
       <c r="AJ6">
-        <v>2.606363636363636</v>
+        <v>3.732777777777778</v>
       </c>
       <c r="AK6">
-        <v>4.948364017833363</v>
+        <v>17.18227793036567</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1166,110 +1160,1717 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Sanofi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SNY</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>40.43999862670898</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>43.40999984741211</v>
+      </c>
+      <c r="F7">
+        <v>50.20000076293945</v>
+      </c>
+      <c r="G7">
+        <v>48.59000015258789</v>
+      </c>
+      <c r="H7">
+        <v>50.09999847412109</v>
+      </c>
+      <c r="I7">
+        <v>48.43000030517578</v>
+      </c>
+      <c r="J7">
+        <v>49.72999954223633</v>
+      </c>
+      <c r="K7">
+        <v>48.22999954223633</v>
+      </c>
+      <c r="L7">
+        <v>48.45999908447266</v>
+      </c>
+      <c r="M7">
+        <v>47.52999877929688</v>
+      </c>
+      <c r="N7">
+        <v>2.037</v>
+      </c>
+      <c r="O7">
+        <v>2.212</v>
+      </c>
+      <c r="P7">
+        <v>1.63</v>
+      </c>
+      <c r="Q7">
+        <v>1.577</v>
+      </c>
+      <c r="R7">
+        <v>1.861</v>
+      </c>
+      <c r="S7">
+        <v>1.739</v>
+      </c>
+      <c r="T7">
+        <v>1.753</v>
+      </c>
+      <c r="U7">
+        <v>1.906</v>
+      </c>
+      <c r="V7">
+        <v>2.044</v>
+      </c>
+      <c r="W7">
+        <v>1.903</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z7">
+        <v>1.8662</v>
+      </c>
+      <c r="AA7">
+        <v>18.662</v>
+      </c>
+      <c r="AB7">
+        <v>40.43999862670898</v>
+      </c>
+      <c r="AC7">
+        <v>47.52999877929688</v>
+      </c>
+      <c r="AD7">
+        <v>7.090000152587891</v>
+      </c>
+      <c r="AE7">
+        <v>25.75200015258789</v>
+      </c>
+      <c r="AF7">
+        <v>2.575200015258789</v>
+      </c>
+      <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
+        <v>522.8299865722656</v>
+      </c>
+      <c r="AI7">
+        <v>12.87600007629394</v>
+      </c>
+      <c r="AJ7">
+        <v>9.331</v>
+      </c>
+      <c r="AK7">
+        <v>22.20700007629394</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chugai Pharmaceutical Co Ltd</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CHGCY</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>4.936666965484619</v>
+      </c>
+      <c r="D8">
+        <v>8.520000457763672</v>
+      </c>
+      <c r="E8">
+        <v>9.672917366027832</v>
+      </c>
+      <c r="F8">
+        <v>15.46416664123535</v>
+      </c>
+      <c r="G8">
+        <v>26.60000038146973</v>
+      </c>
+      <c r="H8">
+        <v>16.36000061035156</v>
+      </c>
+      <c r="I8">
+        <v>12.67000007629395</v>
+      </c>
+      <c r="J8">
+        <v>18.85000038146973</v>
+      </c>
+      <c r="K8">
+        <v>21.96999931335449</v>
+      </c>
+      <c r="L8">
+        <v>26.27000045776367</v>
+      </c>
+      <c r="M8">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="N8">
+        <v>0.189</v>
+      </c>
+      <c r="O8">
+        <v>0.425</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z8">
+        <v>0.307</v>
+      </c>
+      <c r="AA8">
+        <v>0.614</v>
+      </c>
+      <c r="AB8">
+        <v>4.936666965484619</v>
+      </c>
+      <c r="AC8">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="AD8">
+        <v>22.94333219528198</v>
+      </c>
+      <c r="AE8">
+        <v>23.55733219528198</v>
+      </c>
+      <c r="AF8">
+        <v>2.355733219528198</v>
+      </c>
+      <c r="AG8">
+        <v>18</v>
+      </c>
+      <c r="AH8">
+        <v>501.8399848937988</v>
+      </c>
+      <c r="AI8">
+        <v>11.77866609764099</v>
+      </c>
+      <c r="AJ8">
+        <v>1.535</v>
+      </c>
+      <c r="AK8">
+        <v>13.31366609764099</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CVS Health Corp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>78.91000366210938</v>
+      </c>
+      <c r="D9">
+        <v>72.5</v>
+      </c>
+      <c r="E9">
+        <v>65.51999664306641</v>
+      </c>
+      <c r="F9">
+        <v>74.29000091552734</v>
+      </c>
+      <c r="G9">
+        <v>68.30000305175781</v>
+      </c>
+      <c r="H9">
+        <v>103.1600036621094</v>
+      </c>
+      <c r="I9">
+        <v>93.19000244140625</v>
+      </c>
+      <c r="J9">
+        <v>78.95999908447266</v>
+      </c>
+      <c r="K9">
+        <v>44.88999938964844</v>
+      </c>
+      <c r="L9">
+        <v>79.36000061035156</v>
+      </c>
+      <c r="M9">
+        <v>78.86000061035156</v>
+      </c>
+      <c r="N9">
+        <v>2.66</v>
+      </c>
+      <c r="O9">
+        <v>2.66</v>
+      </c>
+      <c r="P9">
+        <v>0.85</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>2.2</v>
+      </c>
+      <c r="W9">
+        <v>2.42</v>
+      </c>
+      <c r="X9">
+        <v>1.33</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z9">
+        <v>2.010909090909091</v>
+      </c>
+      <c r="AA9">
+        <v>22.12</v>
+      </c>
+      <c r="AB9">
+        <v>78.91000366210938</v>
+      </c>
+      <c r="AC9">
+        <v>78.86000061035156</v>
+      </c>
+      <c r="AD9">
+        <v>-0.0500030517578125</v>
+      </c>
+      <c r="AE9">
+        <v>22.06999694824219</v>
+      </c>
+      <c r="AF9">
+        <v>2.206999694824219</v>
+      </c>
+      <c r="AG9">
+        <v>7</v>
+      </c>
+      <c r="AH9">
+        <v>552.0200042724609</v>
+      </c>
+      <c r="AI9">
+        <v>11.03499847412109</v>
+      </c>
+      <c r="AJ9">
+        <v>10.05454545454545</v>
+      </c>
+      <c r="AK9">
+        <v>21.08954392866655</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bristol-Myers Squibb Co</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BMY</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>58.43999862670898</v>
+      </c>
+      <c r="D10">
+        <v>61.27999877929688</v>
+      </c>
+      <c r="E10">
+        <v>51.97999954223633</v>
+      </c>
+      <c r="F10">
+        <v>64.19000244140625</v>
+      </c>
+      <c r="G10">
+        <v>62.02999877929688</v>
+      </c>
+      <c r="H10">
+        <v>62.34999847412109</v>
+      </c>
+      <c r="I10">
+        <v>71.94999694824219</v>
+      </c>
+      <c r="J10">
+        <v>51.31000137329102</v>
+      </c>
+      <c r="K10">
+        <v>56.56000137329102</v>
+      </c>
+      <c r="L10">
+        <v>53.93999862670898</v>
+      </c>
+      <c r="M10">
+        <v>59.02000045776367</v>
+      </c>
+      <c r="N10">
+        <v>2.4</v>
+      </c>
+      <c r="O10">
+        <v>2.48</v>
+      </c>
+      <c r="P10">
+        <v>0.76</v>
+      </c>
+      <c r="Q10">
+        <v>1.56</v>
+      </c>
+      <c r="R10">
+        <v>1.6</v>
+      </c>
+      <c r="S10">
+        <v>1.64</v>
+      </c>
+      <c r="T10">
+        <v>2.29</v>
+      </c>
+      <c r="U10">
+        <v>1.47</v>
+      </c>
+      <c r="V10">
+        <v>2.16</v>
+      </c>
+      <c r="W10">
+        <v>2.28</v>
+      </c>
+      <c r="X10">
+        <v>1.26</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z10">
+        <v>1.809090909090909</v>
+      </c>
+      <c r="AA10">
+        <v>19.9</v>
+      </c>
+      <c r="AB10">
+        <v>58.43999862670898</v>
+      </c>
+      <c r="AC10">
+        <v>59.02000045776367</v>
+      </c>
+      <c r="AD10">
+        <v>0.5800018310546875</v>
+      </c>
+      <c r="AE10">
+        <v>20.48000183105469</v>
+      </c>
+      <c r="AF10">
+        <v>2.048000183105469</v>
+      </c>
+      <c r="AG10">
+        <v>9</v>
+      </c>
+      <c r="AH10">
+        <v>531.180004119873</v>
+      </c>
+      <c r="AI10">
+        <v>10.24000091552734</v>
+      </c>
+      <c r="AJ10">
+        <v>9.045454545454545</v>
+      </c>
+      <c r="AK10">
+        <v>19.28545546098189</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo Company Ltd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DSNKY</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>6.766666889190674</v>
+      </c>
+      <c r="D11">
+        <v>8.713333129882813</v>
+      </c>
+      <c r="E11">
+        <v>10.69999980926514</v>
+      </c>
+      <c r="F11">
+        <v>21.96999931335449</v>
+      </c>
+      <c r="G11">
+        <v>34.63999938964844</v>
+      </c>
+      <c r="H11">
+        <v>25.51000022888184</v>
+      </c>
+      <c r="I11">
+        <v>32.18999862670898</v>
+      </c>
+      <c r="J11">
+        <v>27.35000038146973</v>
+      </c>
+      <c r="K11">
+        <v>27.29000091552734</v>
+      </c>
+      <c r="L11">
+        <v>21.23999977111816</v>
+      </c>
+      <c r="M11">
+        <v>17.43000030517578</v>
+      </c>
+      <c r="N11">
+        <v>0.197</v>
+      </c>
+      <c r="O11">
+        <v>0.207</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z11">
+        <v>0.202</v>
+      </c>
+      <c r="AA11">
+        <v>0.404</v>
+      </c>
+      <c r="AB11">
+        <v>6.766666889190674</v>
+      </c>
+      <c r="AC11">
+        <v>17.43000030517578</v>
+      </c>
+      <c r="AD11">
+        <v>10.66333341598511</v>
+      </c>
+      <c r="AE11">
+        <v>11.06733341598511</v>
+      </c>
+      <c r="AF11">
+        <v>1.106733341598511</v>
+      </c>
+      <c r="AG11">
+        <v>29</v>
+      </c>
+      <c r="AH11">
+        <v>505.4700088500977</v>
+      </c>
+      <c r="AI11">
+        <v>5.533666707992554</v>
+      </c>
+      <c r="AJ11">
+        <v>1.01</v>
+      </c>
+      <c r="AK11">
+        <v>6.543666707992553</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Getinge AB publ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GNGBY</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>16.10000038146973</v>
+      </c>
+      <c r="D12">
+        <v>14.47399997711182</v>
+      </c>
+      <c r="E12">
+        <v>8.975000381469727</v>
+      </c>
+      <c r="F12">
+        <v>18.51000022888184</v>
+      </c>
+      <c r="G12">
+        <v>23.375</v>
+      </c>
+      <c r="H12">
+        <v>43.72999954223633</v>
+      </c>
+      <c r="I12">
+        <v>20.6200008392334</v>
+      </c>
+      <c r="J12">
+        <v>22.23399925231934</v>
+      </c>
+      <c r="K12">
+        <v>16.38500022888184</v>
+      </c>
+      <c r="L12">
+        <v>23.64999961853027</v>
+      </c>
+      <c r="M12">
+        <v>20.44000053405762</v>
+      </c>
+      <c r="N12">
+        <v>0.416</v>
+      </c>
+      <c r="O12">
+        <v>0.478</v>
+      </c>
+      <c r="Q12">
+        <v>3.42</v>
+      </c>
+      <c r="R12">
+        <v>0.191</v>
+      </c>
+      <c r="S12">
+        <v>0.108</v>
+      </c>
+      <c r="T12">
+        <v>0.16</v>
+      </c>
+      <c r="U12">
+        <v>0.362</v>
+      </c>
+      <c r="V12">
+        <v>0.427</v>
+      </c>
+      <c r="W12">
+        <v>0.401</v>
+      </c>
+      <c r="X12">
+        <v>0.502</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z12">
+        <v>0.6465</v>
+      </c>
+      <c r="AA12">
+        <v>6.465</v>
+      </c>
+      <c r="AB12">
+        <v>16.10000038146973</v>
+      </c>
+      <c r="AC12">
+        <v>20.44000053405762</v>
+      </c>
+      <c r="AD12">
+        <v>4.340000152587891</v>
+      </c>
+      <c r="AE12">
+        <v>10.80500015258789</v>
+      </c>
+      <c r="AF12">
+        <v>1.080500015258789</v>
+      </c>
+      <c r="AG12">
+        <v>25</v>
+      </c>
+      <c r="AH12">
+        <v>511.0000133514404</v>
+      </c>
+      <c r="AI12">
+        <v>5.402500076293945</v>
+      </c>
+      <c r="AJ12">
+        <v>3.2325</v>
+      </c>
+      <c r="AK12">
+        <v>8.635000076293945</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pfizer Inc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>30.81593894958496</v>
+      </c>
+      <c r="D13">
+        <v>34.36432647705078</v>
+      </c>
+      <c r="E13">
+        <v>41.41366195678711</v>
+      </c>
+      <c r="F13">
+        <v>37.17267608642578</v>
+      </c>
+      <c r="G13">
+        <v>36.81000137329102</v>
+      </c>
+      <c r="H13">
+        <v>59.04999923706055</v>
+      </c>
+      <c r="I13">
+        <v>51.2400016784668</v>
+      </c>
+      <c r="J13">
+        <v>28.79000091552734</v>
+      </c>
+      <c r="K13">
+        <v>26.53000068664551</v>
+      </c>
+      <c r="L13">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="M13">
+        <v>26.67000007629395</v>
+      </c>
+      <c r="N13">
+        <v>1.68</v>
+      </c>
+      <c r="O13">
+        <v>1.72</v>
+      </c>
+      <c r="P13">
+        <v>0.85389</v>
+      </c>
+      <c r="Q13">
+        <v>1.21442</v>
+      </c>
+      <c r="R13">
+        <v>1.290324</v>
+      </c>
+      <c r="S13">
+        <v>1.366224</v>
+      </c>
+      <c r="T13">
+        <v>1.442124</v>
+      </c>
+      <c r="U13">
+        <v>1.56</v>
+      </c>
+      <c r="V13">
+        <v>1.6</v>
+      </c>
+      <c r="W13">
+        <v>1.64</v>
+      </c>
+      <c r="X13">
+        <v>0.43</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z13">
+        <v>1.345180181818182</v>
+      </c>
+      <c r="AA13">
+        <v>14.796982</v>
+      </c>
+      <c r="AB13">
+        <v>30.81593894958496</v>
+      </c>
+      <c r="AC13">
+        <v>26.67000007629395</v>
+      </c>
+      <c r="AD13">
+        <v>-4.145938873291016</v>
+      </c>
+      <c r="AE13">
+        <v>10.65104312670898</v>
+      </c>
+      <c r="AF13">
+        <v>1.065104312670898</v>
+      </c>
+      <c r="AG13">
+        <v>19</v>
+      </c>
+      <c r="AH13">
+        <v>506.730001449585</v>
+      </c>
+      <c r="AI13">
+        <v>5.325521563354492</v>
+      </c>
+      <c r="AJ13">
+        <v>6.725900909090909</v>
+      </c>
+      <c r="AK13">
+        <v>12.0514224724454</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CSL Ltd</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CSLLY</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>18.13500022888184</v>
+      </c>
+      <c r="D14">
+        <v>27.58499908447266</v>
+      </c>
+      <c r="E14">
+        <v>32.35499954223633</v>
+      </c>
+      <c r="F14">
+        <v>48.625</v>
+      </c>
+      <c r="G14">
+        <v>55.07500076293945</v>
+      </c>
+      <c r="H14">
+        <v>52.90000152587891</v>
+      </c>
+      <c r="I14">
+        <v>48.77000045776367</v>
+      </c>
+      <c r="J14">
+        <v>48.58499908447266</v>
+      </c>
+      <c r="K14">
+        <v>43.77999877929688</v>
+      </c>
+      <c r="L14">
+        <v>28.79999923706055</v>
+      </c>
+      <c r="M14">
+        <v>22.85000038146973</v>
+      </c>
+      <c r="N14">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="O14">
+        <v>0.325</v>
+      </c>
+      <c r="P14">
+        <v>0.17</v>
+      </c>
+      <c r="Q14">
+        <v>0.34</v>
+      </c>
+      <c r="R14">
+        <v>0.43</v>
+      </c>
+      <c r="S14">
+        <v>0.4625</v>
+      </c>
+      <c r="T14">
+        <v>0.505</v>
+      </c>
+      <c r="U14">
+        <v>0.5549999999999999</v>
+      </c>
+      <c r="V14">
+        <v>0.5549999999999999</v>
+      </c>
+      <c r="W14">
+        <v>0.5900000000000001</v>
+      </c>
+      <c r="X14">
+        <v>0.325</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z14">
+        <v>0.4470454545454545</v>
+      </c>
+      <c r="AA14">
+        <v>4.9175</v>
+      </c>
+      <c r="AB14">
+        <v>18.13500022888184</v>
+      </c>
+      <c r="AC14">
+        <v>22.85000038146973</v>
+      </c>
+      <c r="AD14">
+        <v>4.715000152587891</v>
+      </c>
+      <c r="AE14">
+        <v>9.632500152587891</v>
+      </c>
+      <c r="AF14">
+        <v>0.9632500152587891</v>
+      </c>
+      <c r="AG14">
+        <v>22</v>
+      </c>
+      <c r="AH14">
+        <v>502.700008392334</v>
+      </c>
+      <c r="AI14">
+        <v>4.816250076293946</v>
+      </c>
+      <c r="AJ14">
+        <v>2.235227272727273</v>
+      </c>
+      <c r="AK14">
+        <v>7.051477349021218</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Smith &amp; Nephew PLC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SNN</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>30.07999992370605</v>
+      </c>
+      <c r="D15">
+        <v>35.0099983215332</v>
+      </c>
+      <c r="E15">
+        <v>37.38000106811523</v>
+      </c>
+      <c r="F15">
+        <v>48.06999969482422</v>
+      </c>
+      <c r="G15">
+        <v>42.16999816894531</v>
+      </c>
+      <c r="H15">
+        <v>34.61999893188477</v>
+      </c>
+      <c r="I15">
+        <v>26.88999938964844</v>
+      </c>
+      <c r="J15">
+        <v>27.28000068664551</v>
+      </c>
+      <c r="K15">
+        <v>24.57999992370605</v>
+      </c>
+      <c r="L15">
+        <v>32.81000137329102</v>
+      </c>
+      <c r="M15">
+        <v>31.92000007629395</v>
+      </c>
+      <c r="N15">
+        <v>0.75</v>
+      </c>
+      <c r="O15">
+        <v>0.762</v>
+      </c>
+      <c r="P15">
+        <v>0.246</v>
+      </c>
+      <c r="Q15">
+        <v>0.616</v>
+      </c>
+      <c r="R15">
+        <v>0.734</v>
+      </c>
+      <c r="S15">
+        <v>0.728</v>
+      </c>
+      <c r="T15">
+        <v>0.75</v>
+      </c>
+      <c r="U15">
+        <v>0.75</v>
+      </c>
+      <c r="V15">
+        <v>0.75</v>
+      </c>
+      <c r="W15">
+        <v>0.75</v>
+      </c>
+      <c r="X15">
+        <v>0.482</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z15">
+        <v>0.6652727272727272</v>
+      </c>
+      <c r="AA15">
+        <v>7.318</v>
+      </c>
+      <c r="AB15">
+        <v>30.07999992370605</v>
+      </c>
+      <c r="AC15">
+        <v>31.92000007629395</v>
+      </c>
+      <c r="AD15">
+        <v>1.840000152587891</v>
+      </c>
+      <c r="AE15">
+        <v>9.15800015258789</v>
+      </c>
+      <c r="AF15">
+        <v>0.9158000152587891</v>
+      </c>
+      <c r="AG15">
+        <v>16</v>
+      </c>
+      <c r="AH15">
+        <v>510.7200012207031</v>
+      </c>
+      <c r="AI15">
+        <v>4.579000076293945</v>
+      </c>
+      <c r="AJ15">
+        <v>3.326363636363636</v>
+      </c>
+      <c r="AK15">
+        <v>7.905363712657581</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sonic Healthcare Ltd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SKHHY</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>15.35999965667725</v>
+      </c>
+      <c r="D16">
+        <v>17.85000038146973</v>
+      </c>
+      <c r="E16">
+        <v>15.75</v>
+      </c>
+      <c r="F16">
+        <v>20.23999977111816</v>
+      </c>
+      <c r="G16">
+        <v>24.55999946594238</v>
+      </c>
+      <c r="H16">
+        <v>33.63999938964844</v>
+      </c>
+      <c r="I16">
+        <v>20.38999938964844</v>
+      </c>
+      <c r="J16">
+        <v>21.75</v>
+      </c>
+      <c r="K16">
+        <v>16.68000030517578</v>
+      </c>
+      <c r="L16">
+        <v>15.10000038146973</v>
+      </c>
+      <c r="M16">
+        <v>14.27000045776367</v>
+      </c>
+      <c r="N16">
+        <v>0.709</v>
+      </c>
+      <c r="O16">
+        <v>0.276</v>
+      </c>
+      <c r="P16">
+        <v>0.336</v>
+      </c>
+      <c r="Q16">
+        <v>0.604</v>
+      </c>
+      <c r="R16">
+        <v>0.254</v>
+      </c>
+      <c r="S16">
+        <v>0.579</v>
+      </c>
+      <c r="T16">
+        <v>0.59</v>
+      </c>
+      <c r="U16">
+        <v>0.678</v>
+      </c>
+      <c r="V16">
+        <v>0.705</v>
+      </c>
+      <c r="W16">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="X16">
+        <v>0.318</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z16">
+        <v>0.5212727272727272</v>
+      </c>
+      <c r="AA16">
+        <v>5.734</v>
+      </c>
+      <c r="AB16">
+        <v>15.35999965667725</v>
+      </c>
+      <c r="AC16">
+        <v>14.27000045776367</v>
+      </c>
+      <c r="AD16">
+        <v>-1.089999198913574</v>
+      </c>
+      <c r="AE16">
+        <v>4.644000801086426</v>
+      </c>
+      <c r="AF16">
+        <v>0.4644000801086426</v>
+      </c>
+      <c r="AG16">
+        <v>36</v>
+      </c>
+      <c r="AH16">
+        <v>513.7200164794922</v>
+      </c>
+      <c r="AI16">
+        <v>2.322000400543213</v>
+      </c>
+      <c r="AJ16">
+        <v>2.606363636363636</v>
+      </c>
+      <c r="AK16">
+        <v>4.928364036906849</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Medipal Holdings Corp</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MAHLY</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>15.40999984741211</v>
+      </c>
+      <c r="D17">
+        <v>19.67000007629395</v>
+      </c>
+      <c r="E17">
+        <v>21.3799991607666</v>
+      </c>
+      <c r="F17">
+        <v>22.51000022888184</v>
+      </c>
+      <c r="G17">
+        <v>18.72999954223633</v>
+      </c>
+      <c r="H17">
+        <v>18.92000007629395</v>
+      </c>
+      <c r="I17">
+        <v>13.10999965667725</v>
+      </c>
+      <c r="J17">
+        <v>16.39999961853027</v>
+      </c>
+      <c r="K17">
+        <v>16.07999992370605</v>
+      </c>
+      <c r="L17">
+        <v>17.89999961853027</v>
+      </c>
+      <c r="M17">
+        <v>19.10000038146973</v>
+      </c>
+      <c r="N17">
+        <v>0.201</v>
+      </c>
+      <c r="O17">
+        <v>0.222</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z17">
+        <v>0.2115</v>
+      </c>
+      <c r="AA17">
+        <v>0.423</v>
+      </c>
+      <c r="AB17">
+        <v>15.40999984741211</v>
+      </c>
+      <c r="AC17">
+        <v>19.10000038146973</v>
+      </c>
+      <c r="AD17">
+        <v>3.690000534057617</v>
+      </c>
+      <c r="AE17">
+        <v>4.113000534057617</v>
+      </c>
+      <c r="AF17">
+        <v>0.4113000534057617</v>
+      </c>
+      <c r="AG17">
+        <v>27</v>
+      </c>
+      <c r="AH17">
+        <v>515.7000102996826</v>
+      </c>
+      <c r="AI17">
+        <v>2.056500267028809</v>
+      </c>
+      <c r="AJ17">
+        <v>1.0575</v>
+      </c>
+      <c r="AK17">
+        <v>3.114000267028809</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Koninklijke Philips NV</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PHG</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>30.56999969482422</v>
+      </c>
+      <c r="D18">
+        <v>37.79999923706055</v>
+      </c>
+      <c r="E18">
+        <v>35.11000061035156</v>
+      </c>
+      <c r="F18">
+        <v>48.79999923706055</v>
+      </c>
+      <c r="G18">
+        <v>54.16999816894531</v>
+      </c>
+      <c r="H18">
+        <v>36.84999847412109</v>
+      </c>
+      <c r="I18">
+        <v>14.98999977111816</v>
+      </c>
+      <c r="J18">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="K18">
+        <v>25.31999969482422</v>
+      </c>
+      <c r="L18">
+        <v>27.07999992370605</v>
+      </c>
+      <c r="M18">
+        <v>27.6299991607666</v>
+      </c>
+      <c r="O18">
+        <v>0.967</v>
+      </c>
+      <c r="P18">
+        <v>0.883</v>
+      </c>
+      <c r="Q18">
+        <v>0.863</v>
+      </c>
+      <c r="R18">
+        <v>0.992</v>
+      </c>
+      <c r="S18">
+        <v>0.96</v>
+      </c>
+      <c r="U18">
+        <v>1.033</v>
+      </c>
+      <c r="V18">
+        <v>0.964</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z18">
+        <v>0.9517142857142857</v>
+      </c>
+      <c r="AA18">
+        <v>6.662</v>
+      </c>
+      <c r="AB18">
+        <v>30.56999969482422</v>
+      </c>
+      <c r="AC18">
+        <v>27.6299991607666</v>
+      </c>
+      <c r="AD18">
+        <v>-2.940000534057617</v>
+      </c>
+      <c r="AE18">
+        <v>3.721999465942383</v>
+      </c>
+      <c r="AF18">
+        <v>0.3721999465942383</v>
+      </c>
+      <c r="AG18">
+        <v>19</v>
+      </c>
+      <c r="AH18">
+        <v>524.9699840545654</v>
+      </c>
+      <c r="AI18">
+        <v>1.860999732971191</v>
+      </c>
+      <c r="AJ18">
+        <v>4.758571428571429</v>
+      </c>
+      <c r="AK18">
+        <v>6.61957116154262</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Astellas Pharma Inc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ALPMY</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="D19">
+        <v>12.68000030517578</v>
+      </c>
+      <c r="E19">
+        <v>12.53999996185303</v>
+      </c>
+      <c r="F19">
+        <v>17.03000068664551</v>
+      </c>
+      <c r="G19">
+        <v>15.4399995803833</v>
+      </c>
+      <c r="H19">
+        <v>16.27000045776367</v>
+      </c>
+      <c r="I19">
+        <v>15.15999984741211</v>
+      </c>
+      <c r="J19">
+        <v>11.89999961853027</v>
+      </c>
+      <c r="K19">
+        <v>9.659999847412109</v>
+      </c>
+      <c r="L19">
+        <v>13.28999996185303</v>
+      </c>
+      <c r="M19">
+        <v>15.47999954223633</v>
+      </c>
+      <c r="N19">
+        <v>0.247</v>
+      </c>
+      <c r="O19">
+        <v>0.257</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z19">
+        <v>0.252</v>
+      </c>
+      <c r="AA19">
+        <v>0.504</v>
+      </c>
+      <c r="AB19">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="AC19">
+        <v>15.47999954223633</v>
+      </c>
+      <c r="AD19">
+        <v>1.619999885559082</v>
+      </c>
+      <c r="AE19">
+        <v>2.123999885559082</v>
+      </c>
+      <c r="AF19">
+        <v>0.2123999885559082</v>
+      </c>
+      <c r="AG19">
+        <v>33</v>
+      </c>
+      <c r="AH19">
+        <v>510.8399848937988</v>
+      </c>
+      <c r="AI19">
+        <v>1.061999942779541</v>
+      </c>
+      <c r="AJ19">
+        <v>1.26</v>
+      </c>
+      <c r="AK19">
+        <v>2.321999942779541</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Coloplast A/S</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>CLPBY</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C20">
         <v>6.730000019073486</v>
       </c>
-      <c r="D7">
+      <c r="D20">
         <v>7.894999980926514</v>
       </c>
-      <c r="E7">
+      <c r="E20">
         <v>9.25</v>
       </c>
-      <c r="F7">
+      <c r="F20">
         <v>12.39000034332275</v>
       </c>
-      <c r="G7">
+      <c r="G20">
         <v>15.31999969482422</v>
       </c>
-      <c r="H7">
+      <c r="H20">
         <v>17.73900032043457</v>
       </c>
-      <c r="I7">
+      <c r="I20">
         <v>11.63000011444092</v>
       </c>
-      <c r="J7">
+      <c r="J20">
         <v>11.52999973297119</v>
       </c>
-      <c r="K7">
+      <c r="K20">
         <v>10.85999965667725</v>
       </c>
-      <c r="L7">
+      <c r="L20">
         <v>8.5</v>
       </c>
-      <c r="M7">
-        <v>6.559999942779541</v>
-      </c>
-      <c r="Q7">
+      <c r="M20">
+        <v>6.460000038146973</v>
+      </c>
+      <c r="N20">
+        <v>0.311</v>
+      </c>
+      <c r="O20">
+        <v>0.075</v>
+      </c>
+      <c r="S20">
         <v>0.253</v>
       </c>
-      <c r="R7">
+      <c r="T20">
         <v>0.284</v>
       </c>
-      <c r="S7">
+      <c r="U20">
         <v>0.294</v>
       </c>
-      <c r="T7">
+      <c r="V20">
         <v>0.281</v>
       </c>
-      <c r="U7">
+      <c r="W20">
         <v>0.307</v>
       </c>
-      <c r="V7">
-        <v>0.311</v>
-      </c>
-      <c r="W7">
-        <v>0.075</v>
-      </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="Z7">
+      <c r="Z20">
         <v>0.2578571428571428</v>
       </c>
-      <c r="AA7">
+      <c r="AA20">
         <v>1.805</v>
       </c>
-      <c r="AB7">
+      <c r="AB20">
         <v>6.730000019073486</v>
       </c>
-      <c r="AC7">
-        <v>6.559999942779541</v>
-      </c>
-      <c r="AD7">
-        <v>-0.1700000762939453</v>
-      </c>
-      <c r="AE7">
-        <v>1.634999923706055</v>
-      </c>
-      <c r="AF7">
-        <v>0.1634999923706055</v>
-      </c>
-      <c r="AG7">
-        <v>77</v>
-      </c>
-      <c r="AH7">
-        <v>505.1199955940247</v>
-      </c>
-      <c r="AI7">
-        <v>0.8174999618530274</v>
-      </c>
-      <c r="AJ7">
+      <c r="AC20">
+        <v>6.460000038146973</v>
+      </c>
+      <c r="AD20">
+        <v>-0.2699999809265137</v>
+      </c>
+      <c r="AE20">
+        <v>1.535000019073486</v>
+      </c>
+      <c r="AF20">
+        <v>0.1535000019073486</v>
+      </c>
+      <c r="AG20">
+        <v>78</v>
+      </c>
+      <c r="AH20">
+        <v>503.8800029754639</v>
+      </c>
+      <c r="AI20">
+        <v>0.7675000095367432</v>
+      </c>
+      <c r="AJ20">
         <v>1.289285714285714</v>
       </c>
-      <c r="AK7">
-        <v>2.106785676138742</v>
-      </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AK20">
+        <v>2.056785723822458</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cochlear Ltd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CHEOY</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>44.29000091552734</v>
+      </c>
+      <c r="D21">
+        <v>67.09999847412109</v>
+      </c>
+      <c r="E21">
+        <v>62</v>
+      </c>
+      <c r="F21">
+        <v>78.94000244140625</v>
+      </c>
+      <c r="G21">
+        <v>73.76000213623047</v>
+      </c>
+      <c r="H21">
+        <v>78.84999847412109</v>
+      </c>
+      <c r="I21">
+        <v>68.98000335693359</v>
+      </c>
+      <c r="J21">
+        <v>101.3899993896484</v>
+      </c>
+      <c r="K21">
+        <v>89.58999633789063</v>
+      </c>
+      <c r="L21">
+        <v>86.43000030517578</v>
+      </c>
+      <c r="M21">
+        <v>33.84000015258789</v>
+      </c>
+      <c r="N21">
+        <v>1.368</v>
+      </c>
+      <c r="O21">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="P21">
+        <v>0.457</v>
+      </c>
+      <c r="Q21">
+        <v>1.052</v>
+      </c>
+      <c r="R21">
+        <v>1.129</v>
+      </c>
+      <c r="S21">
+        <v>1.149</v>
+      </c>
+      <c r="U21">
+        <v>0.9590000000000001</v>
+      </c>
+      <c r="V21">
+        <v>1.063</v>
+      </c>
+      <c r="W21">
+        <v>1.1</v>
+      </c>
+      <c r="X21">
+        <v>0.76</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="Z21">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="AA21">
+        <v>9.723000000000001</v>
+      </c>
+      <c r="AB21">
+        <v>44.29000091552734</v>
+      </c>
+      <c r="AC21">
+        <v>33.84000015258789</v>
+      </c>
+      <c r="AD21">
+        <v>-10.45000076293945</v>
+      </c>
+      <c r="AE21">
+        <v>-0.7270007629394524</v>
+      </c>
+      <c r="AF21">
+        <v>-0.07270007629394523</v>
+      </c>
+      <c r="AG21">
+        <v>15</v>
+      </c>
+      <c r="AH21">
+        <v>507.6000022888184</v>
+      </c>
+      <c r="AI21">
+        <v>-0.3635003814697262</v>
+      </c>
+      <c r="AJ21">
+        <v>4.8615</v>
+      </c>
+      <c r="AK21">
+        <v>4.497999618530274</v>
+      </c>
+      <c r="AL21" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
